--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -264,41 +264,90 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclatura de semestres</t>
+          <t xml:space="preserve">Sedes nuevas y maduración</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Último semestre observado en la base</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-II</t>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primer semestre proyectable</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclatura de semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Último semestre observado en la base</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primer semestre proyectable</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>
@@ -4293,6 +4342,7 @@
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4306,6 +4356,11 @@
           <t xml:space="preserve">Turnos observados en la sede</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ciclo máximo ofertable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4318,6 +4373,11 @@
           <t xml:space="preserve">Diurno · Noche</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abrió en 2026-I: ciclo 3 en 2027-I, +1 por semestre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4328,6 +4388,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mañana · Noche · Tarde</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan completo</t>
         </is>
       </c>
     </row>

--- a/plantilla_ingresantes.xlsx
+++ b/plantilla_ingresantes.xlsx
@@ -136,7 +136,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. NO se declara el turno: el modelo lo estima con la composición histórica de la sede y la carrera.</t>
+          <t xml:space="preserve">3. NO se declara el turno: el modelo lo estima con la composición histórica de la sede, la carrera y la modalidad.</t>
         </is>
       </c>
     </row>
@@ -205,149 +205,210 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuevos</t>
+          <t xml:space="preserve">Modalidad</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoria. Número entero de ingresantes de esa combinación.</t>
+          <t xml:space="preserve">Recomendada. Presencial, Semi Presencial o A distancia. Si se omite la columna o la celda, el modelo reparte esa fila entre las tres con la composición histórica de su sede y carrera.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nuevos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatoria. Número entero de ingresantes de esa combinación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">CiclosPlan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">Opcional. Ciclos totales del plan de estudios. Sólo hace falta para un programa nuevo cuya duración no sea de 10 ciclos.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Programas nuevos</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Escriba el nombre del nuevo programa en «Carrera» y añada sus ingresantes con normalidad.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al no tener historia propia, el modelo le aplica el comportamiento de continuación del ciclo</t>
+          <t xml:space="preserve">Escriba el nombre del nuevo programa en «Carrera» y añada sus ingresantes con normalidad.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">y de la sede correspondientes, e informa de ello en la pestaña «Ingresantes».</t>
+          <t xml:space="preserve">Al no tener historia propia, el modelo le aplica el comportamiento de continuación del ciclo</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">y de la sede correspondientes, e informa de ello en la pestaña «Ingresantes».</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Si el plan no dura 10 ciclos, indíquelo en «CiclosPlan».</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sedes nuevas y maduración</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por qué conviene declarar la modalidad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+          <t xml:space="preserve">La modalidad cambia el comportamiento del estudiante de forma muy marcada. En el primer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+          <t xml:space="preserve">ciclo, la continuación al semestre siguiente va del 42 % en la modalidad a distancia al 71 %</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+          <t xml:space="preserve">en la presencial, con la semipresencial en medio (56 %). También determina casi por completo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+          <t xml:space="preserve">el turno: a distancia es noche en un 90 %, mientras que presencial es mañana en un 77 %.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nomenclatura de semestres</t>
+          <t xml:space="preserve">Si la columna se deja vacía el modelo estima el reparto, pero la composición está en fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deriva —a distancia pasó del 4,8 % al 19,6 % de la matrícula— y esa estimación arrastra error.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Último semestre observado en la base</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-II</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sedes nuevas y maduración</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primer semestre proyectable</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-I</t>
+          <t xml:space="preserve">Una sede que abre despliega su plan de estudios semestre a semestre: en el de apertura</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t xml:space="preserve">sólo existe el ciclo 1, un semestre después el 2, y así sucesivamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El modelo aplica ese tope automáticamente y avisa si una fila declara ingresantes en un</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ciclo que la sede todavía no imparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si escribe una sede que no figura en el catálogo, se entiende que abre en el primer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semestre en que aparezca en esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclatura de semestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Último semestre observado en la base</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primer semestre proyectable</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formato</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t xml:space="preserve">AAAA-I (primer semestre) · AAAA-II (segundo semestre)</t>
         </is>
@@ -363,9 +424,10 @@
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -386,15 +448,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Modalidad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ciclo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nuevos</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">CiclosPlan</t>
         </is>
@@ -413,14 +480,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E2">
-        <v>730</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>441</v>
       </c>
     </row>
     <row r="3">
@@ -436,14 +508,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>1</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E3">
-        <v>713</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>319</v>
       </c>
     </row>
     <row r="4">
@@ -459,14 +536,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>1</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E4">
-        <v>574</v>
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>317</v>
       </c>
     </row>
     <row r="5">
@@ -482,14 +564,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E5">
-        <v>316</v>
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>297</v>
       </c>
     </row>
     <row r="6">
@@ -505,14 +592,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>1</v>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E6">
-        <v>288</v>
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>279</v>
       </c>
     </row>
     <row r="7">
@@ -523,19 +615,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>1</v>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E7">
-        <v>279</v>
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -546,19 +643,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>1</v>
+          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E8">
-        <v>279</v>
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>217</v>
       </c>
     </row>
     <row r="9">
@@ -574,14 +676,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>1</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E9">
-        <v>243</v>
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -592,19 +699,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>1</v>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E10">
-        <v>228</v>
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -615,19 +727,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E11">
-        <v>217</v>
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -638,19 +755,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E12">
-        <v>215</v>
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -661,19 +783,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>1</v>
+          <t xml:space="preserve">OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E13">
-        <v>211</v>
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>171</v>
       </c>
     </row>
     <row r="14">
@@ -684,19 +811,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>1</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E14">
-        <v>206</v>
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>168</v>
       </c>
     </row>
     <row r="15">
@@ -707,19 +839,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>1</v>
+          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E15">
-        <v>188</v>
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>154</v>
       </c>
     </row>
     <row r="16">
@@ -730,19 +867,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E16">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>147</v>
       </c>
     </row>
     <row r="17">
@@ -753,19 +895,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>1</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E17">
-        <v>167</v>
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>138</v>
       </c>
     </row>
     <row r="18">
@@ -781,14 +928,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>1</v>
+          <t xml:space="preserve">OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E18">
-        <v>164</v>
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -804,14 +956,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E19">
-        <v>154</v>
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -827,14 +984,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E20">
-        <v>148</v>
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>125</v>
       </c>
     </row>
     <row r="21">
@@ -850,14 +1012,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E21">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>117</v>
       </c>
     </row>
     <row r="22">
@@ -873,14 +1040,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E22">
-        <v>134</v>
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>110</v>
       </c>
     </row>
     <row r="23">
@@ -891,19 +1063,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>1</v>
+          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E23">
-        <v>125</v>
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +1091,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E24">
-        <v>115</v>
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>97</v>
       </c>
     </row>
     <row r="25">
@@ -937,19 +1119,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>1</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E25">
-        <v>107</v>
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>94</v>
       </c>
     </row>
     <row r="26">
@@ -965,14 +1152,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E26">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>92</v>
       </c>
     </row>
     <row r="27">
@@ -988,14 +1180,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E27">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>85</v>
       </c>
     </row>
     <row r="28">
@@ -1006,19 +1203,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E28">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>84</v>
       </c>
     </row>
     <row r="29">
@@ -1029,18 +1231,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
         <v>84</v>
       </c>
     </row>
@@ -1057,14 +1264,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E30">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>84</v>
       </c>
     </row>
     <row r="31">
@@ -1080,14 +1292,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>1</v>
+          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E31">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>81</v>
       </c>
     </row>
     <row r="32">
@@ -1103,14 +1320,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E32">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>81</v>
       </c>
     </row>
     <row r="33">
@@ -1121,19 +1343,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>1</v>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E33">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -1149,14 +1376,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E34">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>77</v>
       </c>
     </row>
     <row r="35">
@@ -1172,14 +1404,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>1</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E35">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>77</v>
       </c>
     </row>
     <row r="36">
@@ -1195,14 +1432,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E36">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>76</v>
       </c>
     </row>
     <row r="37">
@@ -1213,19 +1455,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E37">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>74</v>
       </c>
     </row>
     <row r="38">
@@ -1236,19 +1483,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E38">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>66</v>
       </c>
     </row>
     <row r="39">
@@ -1259,19 +1511,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E39">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -1287,14 +1544,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E40">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>61</v>
       </c>
     </row>
     <row r="41">
@@ -1305,19 +1567,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E41">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>58</v>
       </c>
     </row>
     <row r="42">
@@ -1333,14 +1600,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -1351,19 +1623,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>2</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>56</v>
       </c>
     </row>
     <row r="44">
@@ -1374,19 +1651,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>56</v>
       </c>
     </row>
     <row r="45">
@@ -1402,14 +1684,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -1425,14 +1712,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>2</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -1448,14 +1740,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>2</v>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -1466,19 +1763,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>5</v>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>53</v>
       </c>
     </row>
     <row r="49">
@@ -1489,19 +1791,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>51</v>
       </c>
     </row>
     <row r="50">
@@ -1517,14 +1824,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>3</v>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>51</v>
       </c>
     </row>
     <row r="51">
@@ -1540,14 +1852,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>4</v>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>51</v>
       </c>
     </row>
     <row r="52">
@@ -1558,19 +1875,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>2</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -1581,19 +1903,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>2</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>47</v>
       </c>
     </row>
     <row r="54">
@@ -1609,14 +1936,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>2</v>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>47</v>
       </c>
     </row>
     <row r="55">
@@ -1627,19 +1959,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>2</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>44</v>
       </c>
     </row>
     <row r="56">
@@ -1655,14 +1992,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>2</v>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>43</v>
       </c>
     </row>
     <row r="57">
@@ -1678,14 +2020,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>6</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>41</v>
       </c>
     </row>
     <row r="58">
@@ -1701,14 +2048,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -1724,14 +2076,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>6</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -1742,19 +2099,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>7</v>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>38</v>
       </c>
     </row>
     <row r="61">
@@ -1770,14 +2132,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>37</v>
       </c>
     </row>
     <row r="62">
@@ -1793,14 +2160,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>2</v>
+          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>36</v>
       </c>
     </row>
     <row r="63">
@@ -1816,14 +2188,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>35</v>
       </c>
     </row>
     <row r="64">
@@ -1834,19 +2211,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>4</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -1862,14 +2244,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>4</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>29</v>
       </c>
     </row>
     <row r="66">
@@ -1885,15 +2272,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>2</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E66">
         <v>2</v>
       </c>
+      <c r="F66">
+        <v>29</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1908,14 +2300,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>6</v>
+          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>29</v>
       </c>
     </row>
     <row r="68">
@@ -1931,14 +2328,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>4</v>
+          <t xml:space="preserve">INGENIERÍA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -1957,11 +2359,16 @@
           <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
-      <c r="D69">
-        <v>5</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>25</v>
       </c>
     </row>
     <row r="70">
@@ -1977,14 +2384,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>4</v>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -1995,19 +2407,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>4</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E71">
         <v>1</v>
+      </c>
+      <c r="F71">
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -2018,19 +2435,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>7</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E72">
         <v>1</v>
+      </c>
+      <c r="F72">
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -2046,14 +2468,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E73">
         <v>1</v>
+      </c>
+      <c r="F73">
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -2069,14 +2496,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E74">
         <v>1</v>
+      </c>
+      <c r="F74">
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -2087,19 +2519,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>6</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E75">
         <v>1</v>
+      </c>
+      <c r="F75">
+        <v>21</v>
       </c>
     </row>
     <row r="76">
@@ -2115,14 +2552,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>5</v>
+          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E76">
         <v>1</v>
+      </c>
+      <c r="F76">
+        <v>20</v>
       </c>
     </row>
     <row r="77">
@@ -2138,14 +2580,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>5</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F77">
+        <v>18</v>
       </c>
     </row>
     <row r="78">
@@ -2156,19 +2603,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>7</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E78">
         <v>1</v>
+      </c>
+      <c r="F78">
+        <v>17</v>
       </c>
     </row>
     <row r="79">
@@ -2184,14 +2636,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>5</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -2207,14 +2664,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>3</v>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F80">
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -2230,14 +2692,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>5</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F81">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2253,14 +2720,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F82">
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2276,20 +2748,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D83">
-        <v>3</v>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2299,20 +2776,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D84">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E84">
-        <v>424</v>
+        <v>5</v>
+      </c>
+      <c r="F84">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2322,20 +2804,25 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D85">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E85">
-        <v>378</v>
+        <v>2</v>
+      </c>
+      <c r="F85">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2345,20 +2832,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
-        </is>
-      </c>
-      <c r="D86">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E86">
-        <v>285</v>
+        <v>2</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2368,20 +2860,25 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D87">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E87">
-        <v>183</v>
+        <v>3</v>
+      </c>
+      <c r="F87">
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2391,20 +2888,25 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E88">
-        <v>147</v>
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2414,20 +2916,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D89">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E89">
-        <v>127</v>
+        <v>3</v>
+      </c>
+      <c r="F89">
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2437,66 +2944,81 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
-        </is>
-      </c>
-      <c r="D90">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E90">
-        <v>123</v>
+        <v>4</v>
+      </c>
+      <c r="F90">
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D91">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E91">
-        <v>115</v>
+        <v>2</v>
+      </c>
+      <c r="F91">
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D92">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E92">
-        <v>107</v>
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2506,25 +3028,30 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D93">
-        <v>1</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E93">
-        <v>106</v>
+        <v>6</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2532,17 +3059,22 @@
           <t xml:space="preserve">EDUCACIÓN INICIAL</t>
         </is>
       </c>
-      <c r="D94">
-        <v>1</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E94">
-        <v>89</v>
+        <v>2</v>
+      </c>
+      <c r="F94">
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2552,20 +3084,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D95">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E95">
-        <v>84</v>
+        <v>6</v>
+      </c>
+      <c r="F95">
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2575,20 +3112,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D96">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E96">
-        <v>81</v>
+        <v>7</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2598,66 +3140,81 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D97">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E97">
-        <v>78</v>
+        <v>2</v>
+      </c>
+      <c r="F97">
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
-        </is>
-      </c>
-      <c r="D98">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E98">
-        <v>76</v>
+        <v>2</v>
+      </c>
+      <c r="F98">
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
-        </is>
-      </c>
-      <c r="D99">
-        <v>1</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E99">
-        <v>72</v>
+        <v>2</v>
+      </c>
+      <c r="F99">
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2667,43 +3224,53 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D100">
-        <v>1</v>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E100">
-        <v>72</v>
+        <v>2</v>
+      </c>
+      <c r="F100">
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D101">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E101">
-        <v>71</v>
+        <v>2</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2713,66 +3280,81 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D102">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E102">
-        <v>68</v>
+        <v>2</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D103">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E103">
-        <v>67</v>
+        <v>3</v>
+      </c>
+      <c r="F103">
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D104">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E104">
-        <v>66</v>
+        <v>4</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2782,25 +3364,30 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
-        </is>
-      </c>
-      <c r="D105">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E105">
-        <v>62</v>
+        <v>2</v>
+      </c>
+      <c r="F105">
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2808,40 +3395,50 @@
           <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
         </is>
       </c>
-      <c r="D106">
-        <v>1</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E106">
-        <v>61</v>
+        <v>4</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D107">
-        <v>1</v>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E107">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2851,43 +3448,53 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
-        </is>
-      </c>
-      <c r="D108">
-        <v>1</v>
+          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E108">
-        <v>53</v>
+        <v>6</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D109">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E109">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2897,20 +3504,25 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
-        </is>
-      </c>
-      <c r="D110">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E110">
-        <v>32</v>
+        <v>4</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2920,25 +3532,30 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D111">
-        <v>1</v>
+          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E111">
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="F111">
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2946,63 +3563,78 @@
           <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
         </is>
       </c>
-      <c r="D112">
-        <v>1</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E112">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D113">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E113">
-        <v>25</v>
+        <v>4</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="D114">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E114">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3012,20 +3644,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
-        </is>
-      </c>
-      <c r="D115">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E115">
-        <v>24</v>
+        <v>2</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3035,43 +3672,53 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
-        </is>
-      </c>
-      <c r="D116">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E116">
-        <v>24</v>
+        <v>2</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D117">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E117">
-        <v>23</v>
+        <v>2</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3081,43 +3728,53 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D118">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E118">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D119">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E119">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3127,20 +3784,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D120">
-        <v>2</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E120">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3150,20 +3812,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D121">
-        <v>1</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E121">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3173,43 +3840,53 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="D122">
-        <v>1</v>
+          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E122">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
-        </is>
-      </c>
-      <c r="D123">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E123">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3219,20 +3896,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
-        </is>
-      </c>
-      <c r="D124">
-        <v>1</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E124">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3242,20 +3924,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D125">
-        <v>2</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E125">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3265,20 +3952,25 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D126">
-        <v>2</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E126">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3288,20 +3980,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D127">
-        <v>3</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E127">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3314,17 +4011,22 @@
           <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
-      <c r="D128">
-        <v>4</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E128">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3334,20 +4036,25 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D129">
-        <v>3</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E129">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3357,20 +4064,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D130">
-        <v>4</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E130">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3383,17 +4095,22 @@
           <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E131">
         <v>3</v>
       </c>
-      <c r="E131">
-        <v>6</v>
+      <c r="F131">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3403,20 +4120,25 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D132">
-        <v>6</v>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E132">
         <v>5</v>
       </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3426,20 +4148,25 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D133">
-        <v>2</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E133">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3449,20 +4176,25 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
-        </is>
-      </c>
-      <c r="D134">
-        <v>7</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E134">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3472,20 +4204,25 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>2</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E135">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3495,20 +4232,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D136">
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E136">
         <v>2</v>
       </c>
-      <c r="E136">
-        <v>4</v>
+      <c r="F136">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3518,20 +4260,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D137">
-        <v>2</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3541,20 +4288,25 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D138">
-        <v>2</v>
+          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E138">
         <v>2</v>
       </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3564,20 +4316,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D139">
-        <v>5</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E139">
         <v>2</v>
       </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-II</t>
+          <t xml:space="preserve">2027-I</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3587,15 +4344,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D140">
-        <v>2</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E140">
         <v>2</v>
       </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3610,14 +4372,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D141">
-        <v>2</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <v>324</v>
       </c>
     </row>
     <row r="142">
@@ -3633,14 +4400,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D142">
-        <v>2</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>244</v>
       </c>
     </row>
     <row r="143">
@@ -3656,14 +4428,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D143">
-        <v>3</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E143">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F143">
+        <v>165</v>
       </c>
     </row>
     <row r="144">
@@ -3674,19 +4451,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D144">
-        <v>4</v>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F144">
+        <v>115</v>
       </c>
     </row>
     <row r="145">
@@ -3702,14 +4484,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
-        </is>
-      </c>
-      <c r="D145">
-        <v>4</v>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E145">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F145">
+        <v>114</v>
       </c>
     </row>
     <row r="146">
@@ -3725,14 +4512,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
-        </is>
-      </c>
-      <c r="D146">
-        <v>2</v>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F146">
+        <v>106</v>
       </c>
     </row>
     <row r="147">
@@ -3748,14 +4540,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D147">
-        <v>2</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F147">
+        <v>96</v>
       </c>
     </row>
     <row r="148">
@@ -3766,19 +4563,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D148">
-        <v>2</v>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E148">
         <v>1</v>
+      </c>
+      <c r="F148">
+        <v>95</v>
       </c>
     </row>
     <row r="149">
@@ -3789,19 +4591,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Norte</t>
+          <t xml:space="preserve">Lima Sur</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D149">
-        <v>2</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E149">
         <v>1</v>
+      </c>
+      <c r="F149">
+        <v>78</v>
       </c>
     </row>
     <row r="150">
@@ -3817,14 +4624,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
-        </is>
-      </c>
-      <c r="D150">
-        <v>2</v>
+          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E150">
         <v>1</v>
+      </c>
+      <c r="F150">
+        <v>76</v>
       </c>
     </row>
     <row r="151">
@@ -3840,14 +4652,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
-        </is>
-      </c>
-      <c r="D151">
-        <v>2</v>
+          <t xml:space="preserve">OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E151">
         <v>1</v>
+      </c>
+      <c r="F151">
+        <v>72</v>
       </c>
     </row>
     <row r="152">
@@ -3863,14 +4680,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D152">
-        <v>6</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E152">
         <v>1</v>
+      </c>
+      <c r="F152">
+        <v>72</v>
       </c>
     </row>
     <row r="153">
@@ -3881,19 +4703,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="D153">
-        <v>7</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E153">
         <v>1</v>
+      </c>
+      <c r="F153">
+        <v>67</v>
       </c>
     </row>
     <row r="154">
@@ -3909,14 +4736,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D154">
-        <v>3</v>
+          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E154">
         <v>1</v>
+      </c>
+      <c r="F154">
+        <v>62</v>
       </c>
     </row>
     <row r="155">
@@ -3927,19 +4759,24 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D155">
-        <v>4</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E155">
         <v>1</v>
+      </c>
+      <c r="F155">
+        <v>57</v>
       </c>
     </row>
     <row r="156">
@@ -3955,14 +4792,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="D156">
-        <v>5</v>
+          <t xml:space="preserve">OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E156">
         <v>1</v>
+      </c>
+      <c r="F156">
+        <v>53</v>
       </c>
     </row>
     <row r="157">
@@ -3978,14 +4820,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="D157">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E157">
         <v>1</v>
+      </c>
+      <c r="F157">
+        <v>52</v>
       </c>
     </row>
     <row r="158">
@@ -4001,14 +4848,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="D158">
-        <v>10</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E158">
         <v>1</v>
+      </c>
+      <c r="F158">
+        <v>51</v>
       </c>
     </row>
     <row r="159">
@@ -4024,14 +4876,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="D159">
-        <v>2</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E159">
         <v>1</v>
+      </c>
+      <c r="F159">
+        <v>51</v>
       </c>
     </row>
     <row r="160">
@@ -4047,14 +4904,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="D160">
-        <v>5</v>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E160">
         <v>1</v>
+      </c>
+      <c r="F160">
+        <v>50</v>
       </c>
     </row>
     <row r="161">
@@ -4070,14 +4932,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
-        </is>
-      </c>
-      <c r="D161">
-        <v>5</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E161">
         <v>1</v>
+      </c>
+      <c r="F161">
+        <v>49</v>
       </c>
     </row>
     <row r="162">
@@ -4093,14 +4960,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D162">
-        <v>3</v>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E162">
         <v>1</v>
+      </c>
+      <c r="F162">
+        <v>48</v>
       </c>
     </row>
     <row r="163">
@@ -4116,14 +4988,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
-        </is>
-      </c>
-      <c r="D163">
-        <v>4</v>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E163">
         <v>1</v>
+      </c>
+      <c r="F163">
+        <v>46</v>
       </c>
     </row>
     <row r="164">
@@ -4139,14 +5016,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
-        </is>
-      </c>
-      <c r="D164">
-        <v>2</v>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E164">
         <v>1</v>
+      </c>
+      <c r="F164">
+        <v>42</v>
       </c>
     </row>
     <row r="165">
@@ -4162,14 +5044,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D165">
-        <v>3</v>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E165">
         <v>1</v>
+      </c>
+      <c r="F165">
+        <v>41</v>
       </c>
     </row>
     <row r="166">
@@ -4180,19 +5067,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
-        </is>
-      </c>
-      <c r="D166">
-        <v>4</v>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E166">
         <v>1</v>
+      </c>
+      <c r="F166">
+        <v>40</v>
       </c>
     </row>
     <row r="167">
@@ -4203,19 +5095,24 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="D167">
-        <v>4</v>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E167">
         <v>1</v>
+      </c>
+      <c r="F167">
+        <v>40</v>
       </c>
     </row>
     <row r="168">
@@ -4226,19 +5123,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D168">
-        <v>4</v>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E168">
         <v>1</v>
+      </c>
+      <c r="F168">
+        <v>40</v>
       </c>
     </row>
     <row r="169">
@@ -4254,14 +5156,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="D169">
-        <v>3</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
       <c r="E169">
         <v>1</v>
+      </c>
+      <c r="F169">
+        <v>40</v>
       </c>
     </row>
     <row r="170">
@@ -4280,11 +5187,16 @@
           <t xml:space="preserve">PSICOLOGÍA</t>
         </is>
       </c>
-      <c r="D170">
-        <v>4</v>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
       <c r="E170">
         <v>1</v>
+      </c>
+      <c r="F170">
+        <v>38</v>
       </c>
     </row>
     <row r="171">
@@ -4295,19 +5207,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lima Sur</t>
+          <t xml:space="preserve">Lima Norte</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="D171">
-        <v>5</v>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
       <c r="E171">
         <v>1</v>
+      </c>
+      <c r="F171">
+        <v>37</v>
       </c>
     </row>
     <row r="172">
@@ -4323,13 +5240,2958 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="F175">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="F176">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="F177">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="F180">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+      <c r="F182">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="F188">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="F191">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
           <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
         </is>
       </c>
-      <c r="D172">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+      <c r="F195">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="F197">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+      <c r="F198">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+      <c r="F199">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+      <c r="F200">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E202">
+        <v>2</v>
+      </c>
+      <c r="F202">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+      <c r="F203">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+      <c r="F204">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="F205">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E207">
+        <v>2</v>
+      </c>
+      <c r="F207">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+      <c r="F209">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+      <c r="F210">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+      <c r="F211">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
+      <c r="F212">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E213">
+        <v>2</v>
+      </c>
+      <c r="F213">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E214">
+        <v>2</v>
+      </c>
+      <c r="F214">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E215">
         <v>3</v>
       </c>
-      <c r="E172">
+      <c r="F215">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E216">
+        <v>3</v>
+      </c>
+      <c r="F216">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E217">
+        <v>4</v>
+      </c>
+      <c r="F217">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E218">
+        <v>2</v>
+      </c>
+      <c r="F218">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E219">
+        <v>6</v>
+      </c>
+      <c r="F219">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E220">
+        <v>7</v>
+      </c>
+      <c r="F220">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E221">
+        <v>2</v>
+      </c>
+      <c r="F221">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E222">
+        <v>2</v>
+      </c>
+      <c r="F222">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E223">
+        <v>3</v>
+      </c>
+      <c r="F223">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E224">
+        <v>3</v>
+      </c>
+      <c r="F224">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E225">
+        <v>2</v>
+      </c>
+      <c r="F225">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E226">
+        <v>2</v>
+      </c>
+      <c r="F226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E227">
+        <v>4</v>
+      </c>
+      <c r="F227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E228">
+        <v>5</v>
+      </c>
+      <c r="F228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E229">
+        <v>4</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E230">
+        <v>3</v>
+      </c>
+      <c r="F230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E231">
+        <v>4</v>
+      </c>
+      <c r="F231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E232">
+        <v>2</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E233">
+        <v>2</v>
+      </c>
+      <c r="F233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E234">
+        <v>2</v>
+      </c>
+      <c r="F234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E235">
+        <v>2</v>
+      </c>
+      <c r="F235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E236">
+        <v>4</v>
+      </c>
+      <c r="F236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E237">
+        <v>4</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E238">
+        <v>2</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+      <c r="F239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E240">
+        <v>2</v>
+      </c>
+      <c r="F240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E241">
+        <v>2</v>
+      </c>
+      <c r="F241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E242">
+        <v>2</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E243">
+        <v>2</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E244">
+        <v>2</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Norte</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E245">
+        <v>2</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E246">
+        <v>6</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E247">
+        <v>7</v>
+      </c>
+      <c r="F247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E248">
+        <v>3</v>
+      </c>
+      <c r="F248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E249">
+        <v>3</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E250">
+        <v>4</v>
+      </c>
+      <c r="F250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E251">
+        <v>5</v>
+      </c>
+      <c r="F251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E252">
+        <v>3</v>
+      </c>
+      <c r="F252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E253">
+        <v>3</v>
+      </c>
+      <c r="F253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E254">
+        <v>3</v>
+      </c>
+      <c r="F254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E255">
+        <v>10</v>
+      </c>
+      <c r="F255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E256">
+        <v>5</v>
+      </c>
+      <c r="F256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E257">
+        <v>2</v>
+      </c>
+      <c r="F257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E258">
+        <v>4</v>
+      </c>
+      <c r="F258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E259">
+        <v>5</v>
+      </c>
+      <c r="F259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E260">
+        <v>3</v>
+      </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E261">
+        <v>4</v>
+      </c>
+      <c r="F261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E262">
+        <v>4</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E263">
+        <v>2</v>
+      </c>
+      <c r="F263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E264">
+        <v>3</v>
+      </c>
+      <c r="F264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERECHO</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E265">
+        <v>6</v>
+      </c>
+      <c r="F265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E266">
+        <v>3</v>
+      </c>
+      <c r="F266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E267">
+        <v>4</v>
+      </c>
+      <c r="F267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E268">
+        <v>2</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E269">
+        <v>2</v>
+      </c>
+      <c r="F269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E270">
+        <v>3</v>
+      </c>
+      <c r="F270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E271">
+        <v>4</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E272">
+        <v>4</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E273">
+        <v>4</v>
+      </c>
+      <c r="F273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E274">
+        <v>3</v>
+      </c>
+      <c r="F274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia</t>
+        </is>
+      </c>
+      <c r="E275">
+        <v>4</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
+      </c>
+      <c r="E276">
+        <v>5</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-II</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lima Sur</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+      <c r="E277">
+        <v>3</v>
+      </c>
+      <c r="F277">
         <v>1</v>
       </c>
     </row>
@@ -4387,7 +8249,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mañana · Noche · Tarde</t>
+          <t xml:space="preserve">Tarde · Mañana · Noche</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4399,263 +8261,421 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carreras</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ciclos del plan</t>
+          <t xml:space="preserve">Modalidades</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>10</v>
+          <t xml:space="preserve">A distancia</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>10</v>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>10</v>
+          <t xml:space="preserve">Semi Presencial</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>10</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carreras</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ciclos del plan</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modalidades con historia en la base</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
+          <t xml:space="preserve">ADMINISTRACIÓN DE EMPRESAS</t>
         </is>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTABILIDAD</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y FINANZAS</t>
         </is>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DERECHO</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y MARKETING</t>
         </is>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
+          <t xml:space="preserve">ADMINISTRACIÓN Y NEGOCIOS INTERNACIONALES</t>
         </is>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
+          <t xml:space="preserve">ARQUITECTURA</t>
         </is>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
+          <t xml:space="preserve">CIENCIAS DE LA COMUNICACIÓN</t>
         </is>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENFERMERÍA</t>
+          <t xml:space="preserve">CONTABILIDAD</t>
         </is>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
+          <t xml:space="preserve">DERECHO</t>
         </is>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA AMBIENTAL</t>
+          <t xml:space="preserve">DISEÑO GRÁFICO DIGITAL Y PUBLICITARIO</t>
         </is>
       </c>
       <c r="B19">
         <v>10</v>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA BIOMÉDICA</t>
+          <t xml:space="preserve">EDUCACIÓN INICIAL</t>
         </is>
       </c>
       <c r="B20">
         <v>10</v>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA CIVIL</t>
+          <t xml:space="preserve">EDUCACIÓN PRIMARIA</t>
         </is>
       </c>
       <c r="B21">
         <v>10</v>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
+          <t xml:space="preserve">ENFERMERÍA</t>
         </is>
       </c>
       <c r="B22">
         <v>10</v>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
+          <t xml:space="preserve">FARMACIA Y BIOQUÍMICA</t>
         </is>
       </c>
       <c r="B23">
         <v>10</v>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
+          <t xml:space="preserve">INGENIERÍA AMBIENTAL</t>
         </is>
       </c>
       <c r="B24">
         <v>10</v>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
+          <t xml:space="preserve">INGENIERÍA BIOMÉDICA</t>
         </is>
       </c>
       <c r="B25">
         <v>10</v>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
+          <t xml:space="preserve">INGENIERÍA CIVIL</t>
         </is>
       </c>
       <c r="B26">
         <v>10</v>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSTETRICIA</t>
+          <t xml:space="preserve">INGENIERÍA DE SISTEMAS</t>
         </is>
       </c>
       <c r="B27">
         <v>10</v>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSICOLOGÍA</t>
+          <t xml:space="preserve">INGENIERÍA DE SOFTWARE</t>
         </is>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
+          <t xml:space="preserve">INGENIERÍA INDUSTRIAL</t>
         </is>
       </c>
       <c r="B29">
         <v>10</v>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+          <t xml:space="preserve">INGENIERÍA MECATRÓNICA</t>
         </is>
       </c>
       <c r="B30">
         <v>10</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial · Semi Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUTRICIÓN Y DIETÉTICA</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial · Semi Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>11</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A distancia · Presencial · Semi Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN LABORATORIO CLÍNICO Y ANATOMÍA PATOLÓGICA</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>10</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TECNOLOGÍA MÉDICA EN TERAPIA FÍSICA Y REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presencial</t>
+        </is>
       </c>
     </row>
   </sheetData>
